--- a/docs/iFare_AI任務看板.xlsx
+++ b/docs/iFare_AI任務看板.xlsx
@@ -1,33 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emma.chung\ifare-website\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE14645-516D-47F8-A383-AF8309F5102A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -111,16 +105,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -148,10 +146,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -476,10 +482,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -568,8 +579,10 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError sqref="A1:N2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/iFare_AI任務看板.xlsx
+++ b/docs/iFare_AI任務看板.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emma.chung\ifare-website\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE14645-516D-47F8-A383-AF8309F5102A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
   <si>
     <t>task_id</t>
   </si>
@@ -100,25 +106,93 @@
   </si>
   <si>
     <t>backend-admin</t>
+  </si>
+  <si>
+    <t>TASK-2026-05-26-002</t>
+  </si>
+  <si>
+    <t>後台 AI 維護中心 nextAction 是「需人工處理」的任務</t>
+  </si>
+  <si>
+    <t>後台 AI 維護中心 nextAction 是「需人工處理」的任務，UI 上的「執行」按鈕應該 disable 並顯示提示，避免使用者點下去後任務直接變 failed</t>
+  </si>
+  <si>
+    <t>2026-05-26 17:48:09</t>
+  </si>
+  <si>
+    <t>emma</t>
+  </si>
+  <si>
+    <t>TASK-2026-05-26-003</t>
+  </si>
+  <si>
+    <t>收件匣的 pending_review 任務若超過 3 天沒人處理</t>
+  </si>
+  <si>
+    <t>meta</t>
+  </si>
+  <si>
+    <t>收件匣的 pending_review 任務若超過 3 天沒人處理，卡片應該標紅色「超時」警示，避免任務積壓被遺忘</t>
+  </si>
+  <si>
+    <t>分類為「雜項維護」、優先級「中」，建議動作：需人工處理。</t>
+  </si>
+  <si>
+    <t>TASK-2026-05-26-004</t>
+  </si>
+  <si>
+    <t>runner 連線到舊版本端點時前端只顯示「not found」</t>
+  </si>
+  <si>
+    <t>runner 連線到舊版本端點時前端只顯示「not found」，應改成提示「runner 可能版本太舊，請在專案根目錄重啟 npm run agent:runner」</t>
+  </si>
+  <si>
+    <t>TASK-2026-05-26-005</t>
+  </si>
+  <si>
+    <t>AI 維護報告的高優先待辦清單</t>
+  </si>
+  <si>
+    <t>report-ops</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>AI 維護報告的高優先待辦清單，後台應提供「批次匯入到任務收件匣」按鈕，把報告的 20 筆後臺優化高優先項目一鍵變成 pending_review 任務卡</t>
+  </si>
+  <si>
+    <t>分類為「報告產出」、優先級「高」，建議動作：需人工處理。</t>
+  </si>
+  <si>
+    <t>TASK-2026-05-26-006</t>
+  </si>
+  <si>
+    <t>audit log 出現 failed 紀錄時應自動發送通知（LINE Not…</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>audit log 出現 failed 紀錄時應自動發送通知（LINE Notify 或 email），避免週末跑出來的失敗任務沒人發現，造成處理積壓</t>
+  </si>
+  <si>
+    <t>分類為「雜項維護」、優先級「中」，建議動作：查詢執行紀錄。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -146,18 +220,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -482,15 +548,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N7"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -578,11 +639,229 @@
         <v>23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
   </ignoredErrors>
 </worksheet>
 </file>